--- a/07_marketing_leads.xlsx
+++ b/07_marketing_leads.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="268">
   <si>
     <t>lead_id</t>
   </si>
@@ -482,6 +482,339 @@
   </si>
   <si>
     <t>Финансист Ф.Ф.</t>
+  </si>
+  <si>
+    <t>L051</t>
+  </si>
+  <si>
+    <t>"ООО ""Ромашка"""</t>
+  </si>
+  <si>
+    <t>L052</t>
+  </si>
+  <si>
+    <t>"АО ""ТехноСервис"""</t>
+  </si>
+  <si>
+    <t>L053</t>
+  </si>
+  <si>
+    <t>april_newsletter</t>
+  </si>
+  <si>
+    <t>L054</t>
+  </si>
+  <si>
+    <t>"ООО ""Ромашка-Логистик"""</t>
+  </si>
+  <si>
+    <t>L055</t>
+  </si>
+  <si>
+    <t>"ЗАО ""СтройИнвест"""</t>
+  </si>
+  <si>
+    <t>L056</t>
+  </si>
+  <si>
+    <t>"ООО ""Айти-Решения"""</t>
+  </si>
+  <si>
+    <t>L057</t>
+  </si>
+  <si>
+    <t>"ООО ""Торговый Дом"""</t>
+  </si>
+  <si>
+    <t>L058</t>
+  </si>
+  <si>
+    <t>"ООО ""Бизнес-Консалт"""</t>
+  </si>
+  <si>
+    <t>L059</t>
+  </si>
+  <si>
+    <t>"АО ""ФинансГрупп"""</t>
+  </si>
+  <si>
+    <t>L060</t>
+  </si>
+  <si>
+    <t>"ООО ""ПромТех"""</t>
+  </si>
+  <si>
+    <t>L061</t>
+  </si>
+  <si>
+    <t>"ООО ""МедиаХолдинг"""</t>
+  </si>
+  <si>
+    <t>L062</t>
+  </si>
+  <si>
+    <t>"АО ""ЭнергоСбыт"""</t>
+  </si>
+  <si>
+    <t>partner_petrov</t>
+  </si>
+  <si>
+    <t>L063</t>
+  </si>
+  <si>
+    <t>"ООО ""ЛогистикПлюс"""</t>
+  </si>
+  <si>
+    <t>L064</t>
+  </si>
+  <si>
+    <t>ИП Петрова</t>
+  </si>
+  <si>
+    <t>Петрова П.П.</t>
+  </si>
+  <si>
+    <t>L065</t>
+  </si>
+  <si>
+    <t>"ООО ""Трейд"""</t>
+  </si>
+  <si>
+    <t>retail_forum</t>
+  </si>
+  <si>
+    <t>L066</t>
+  </si>
+  <si>
+    <t>"ООО ""Новые Технологии"""</t>
+  </si>
+  <si>
+    <t>L067</t>
+  </si>
+  <si>
+    <t>"АО ""Цифровые Решения"""</t>
+  </si>
+  <si>
+    <t>Цифров Ц.Ц.</t>
+  </si>
+  <si>
+    <t>L068</t>
+  </si>
+  <si>
+    <t>"ООО ""Бизнес-Партнер"""</t>
+  </si>
+  <si>
+    <t>Партнеров П.П.</t>
+  </si>
+  <si>
+    <t>L069</t>
+  </si>
+  <si>
+    <t>L070</t>
+  </si>
+  <si>
+    <t>"ООО ""Инновации"""</t>
+  </si>
+  <si>
+    <t>Иннов И.И.</t>
+  </si>
+  <si>
+    <t>june_newsletter</t>
+  </si>
+  <si>
+    <t>L071</t>
+  </si>
+  <si>
+    <t>"АО ""СтройТех"""</t>
+  </si>
+  <si>
+    <t>Строев Т.Т.</t>
+  </si>
+  <si>
+    <t>L072</t>
+  </si>
+  <si>
+    <t>"ООО ""МаркетингПро"""</t>
+  </si>
+  <si>
+    <t>marketing_forum</t>
+  </si>
+  <si>
+    <t>L073</t>
+  </si>
+  <si>
+    <t>"ООО ""ЭнергоПром"""</t>
+  </si>
+  <si>
+    <t>Энергов П.П.</t>
+  </si>
+  <si>
+    <t>L074</t>
+  </si>
+  <si>
+    <t>"АО ""ЛогистикСистем"""</t>
+  </si>
+  <si>
+    <t>Логов С.С.</t>
+  </si>
+  <si>
+    <t>L075</t>
+  </si>
+  <si>
+    <t>"ООО ""ФинТех"""</t>
+  </si>
+  <si>
+    <t>L076</t>
+  </si>
+  <si>
+    <t>ИП Козлов</t>
+  </si>
+  <si>
+    <t>Козлов К.К.</t>
+  </si>
+  <si>
+    <t>L077</t>
+  </si>
+  <si>
+    <t>"ООО ""РитейлГрупп"""</t>
+  </si>
+  <si>
+    <t>L078</t>
+  </si>
+  <si>
+    <t>"АО ""МедиаХолдинг-2"""</t>
+  </si>
+  <si>
+    <t>L079</t>
+  </si>
+  <si>
+    <t>"ООО ""КонсалтБюро"""</t>
+  </si>
+  <si>
+    <t>L080</t>
+  </si>
+  <si>
+    <t>"ООО ""ПромАвтоматика"""</t>
+  </si>
+  <si>
+    <t>Промов А.А.</t>
+  </si>
+  <si>
+    <t>L081</t>
+  </si>
+  <si>
+    <t>"АО ""ИТ-Сервис"""</t>
+  </si>
+  <si>
+    <t>Сервисов С.С.</t>
+  </si>
+  <si>
+    <t>L082</t>
+  </si>
+  <si>
+    <t>"ООО ""Торговый Дом-2"""</t>
+  </si>
+  <si>
+    <t>Торгов Т.Д.</t>
+  </si>
+  <si>
+    <t>L083</t>
+  </si>
+  <si>
+    <t>ИП Николаев</t>
+  </si>
+  <si>
+    <t>L084</t>
+  </si>
+  <si>
+    <t>"ООО ""СтройИнвест-Юг"""</t>
+  </si>
+  <si>
+    <t>Строев Ю.Ю.</t>
+  </si>
+  <si>
+    <t>august_newsletter</t>
+  </si>
+  <si>
+    <t>L085</t>
+  </si>
+  <si>
+    <t>"АО ""ЭнергоСбыт-2"""</t>
+  </si>
+  <si>
+    <t>Энергов Э.2.</t>
+  </si>
+  <si>
+    <t>L086</t>
+  </si>
+  <si>
+    <t>"ООО ""ЛогистикПлюс-Юг"""</t>
+  </si>
+  <si>
+    <t>Логов Ю.Ю.</t>
+  </si>
+  <si>
+    <t>L087</t>
+  </si>
+  <si>
+    <t>"ООО ""ФинКонсалт"""</t>
+  </si>
+  <si>
+    <t>Финансов К.К.</t>
+  </si>
+  <si>
+    <t>L088</t>
+  </si>
+  <si>
+    <t>"АО ""ТехноСервис-2"""</t>
+  </si>
+  <si>
+    <t>Технов Т.2.</t>
+  </si>
+  <si>
+    <t>L089</t>
+  </si>
+  <si>
+    <t>"ООО ""Медиа-Юг"""</t>
+  </si>
+  <si>
+    <t>Медиа Ю.Ю.</t>
+  </si>
+  <si>
+    <t>L090</t>
+  </si>
+  <si>
+    <t>ИП Васильев</t>
+  </si>
+  <si>
+    <t>L091</t>
+  </si>
+  <si>
+    <t>L092</t>
+  </si>
+  <si>
+    <t>L093</t>
+  </si>
+  <si>
+    <t>L094</t>
+  </si>
+  <si>
+    <t>L095</t>
+  </si>
+  <si>
+    <t>L096</t>
+  </si>
+  <si>
+    <t>L097</t>
+  </si>
+  <si>
+    <t>L098</t>
+  </si>
+  <si>
+    <t>L099</t>
+  </si>
+  <si>
+    <t>L100</t>
   </si>
 </sst>
 </file>
@@ -491,7 +824,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -499,15 +832,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="12.0"/>
       <color rgb="FF0F1115"/>
-      <name val="Quote-cjk-patch"/>
+      <name val="&quot;Segoe UI&quot;"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12.0"/>
-      <color rgb="FF0F1115"/>
-      <name val="Quote-cjk-patch"/>
+      <color theme="1"/>
+      <name val="&quot;Segoe UI&quot;"/>
     </font>
   </fonts>
   <fills count="3">
@@ -524,13 +861,8 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border/>
-    <border>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
@@ -539,17 +871,19 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -767,11 +1101,14 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="34.25"/>
-    <col customWidth="1" min="3" max="3" width="13.0"/>
-    <col customWidth="1" min="5" max="5" width="18.38"/>
-    <col customWidth="1" min="6" max="6" width="32.38"/>
-    <col customWidth="1" min="8" max="8" width="51.0"/>
+    <col customWidth="1" min="1" max="1" width="7.5"/>
+    <col customWidth="1" min="2" max="2" width="27.88"/>
+    <col customWidth="1" min="3" max="3" width="18.63"/>
+    <col customWidth="1" min="4" max="4" width="10.88"/>
+    <col customWidth="1" min="5" max="5" width="20.63"/>
+    <col customWidth="1" min="6" max="6" width="11.25"/>
+    <col customWidth="1" min="7" max="7" width="6.5"/>
+    <col customWidth="1" min="8" max="8" width="9.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -801,1298 +1138,2598 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>45453.0</v>
       </c>
-      <c r="G2" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>45458.0</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>35000.0</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>45463.0</v>
       </c>
-      <c r="G4" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>45478.0</v>
       </c>
-      <c r="G5" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="G5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>45491.0</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>5000.0</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>45493.0</v>
       </c>
-      <c r="G7" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="G7" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>45498.0</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <v>15000.0</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>45506.0</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <v>35000.0</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>45514.0</v>
       </c>
-      <c r="G10" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="G10" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>45519.0</v>
       </c>
-      <c r="G11" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="G11" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>45524.0</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>15000.0</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="2" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>45540.0</v>
       </c>
-      <c r="G13" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="G13" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>45545.0</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>35000.0</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>45550.0</v>
       </c>
-      <c r="G15" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="G15" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>45557.0</v>
       </c>
-      <c r="G16" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="G16" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>45563.0</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="1">
         <v>5000.0</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>45570.0</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="1">
         <v>15000.0</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>45577.0</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="1">
         <v>35000.0</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <v>45583.0</v>
       </c>
-      <c r="G20" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="2" t="s">
+      <c r="G20" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>45590.0</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="1">
         <v>5000.0</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <v>45598.0</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="1">
         <v>35000.0</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <v>45604.0</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="1">
         <v>15000.0</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <v>45611.0</v>
       </c>
-      <c r="G24" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H24" s="2" t="s">
+      <c r="G24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <v>45616.0</v>
       </c>
-      <c r="G25" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="2" t="s">
+      <c r="G25" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
         <v>45621.0</v>
       </c>
-      <c r="G26" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H26" s="2" t="s">
+      <c r="G26" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <v>45628.0</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="1">
         <v>5000.0</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="2">
         <v>45634.0</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="1">
         <v>35000.0</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="2">
         <v>45641.0</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="1">
         <v>15000.0</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="2">
         <v>45646.0</v>
       </c>
-      <c r="G30" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="G30" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <v>45651.0</v>
       </c>
-      <c r="G31" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="G31" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>45667.0</v>
       </c>
-      <c r="G32" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="2" t="s">
+      <c r="G32" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="2">
         <v>45672.0</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33" s="1">
         <v>35000.0</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="2">
         <v>45677.0</v>
       </c>
-      <c r="G34" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="2" t="s">
+      <c r="G34" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
         <v>45693.0</v>
       </c>
-      <c r="G35" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="G35" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="2">
         <v>45706.0</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="1">
         <v>5000.0</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="2">
         <v>45708.0</v>
       </c>
-      <c r="G37" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H37" s="2" t="s">
+      <c r="G37" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="2">
         <v>45713.0</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38" s="1">
         <v>15000.0</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="2">
         <v>45716.0</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="1">
         <v>35000.0</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="2">
         <v>45717.0</v>
       </c>
-      <c r="G40" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H40" s="2" t="s">
+      <c r="G40" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="2">
         <v>45721.0</v>
       </c>
-      <c r="G41" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H41" s="2" t="s">
+      <c r="G41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="2">
         <v>45726.0</v>
       </c>
-      <c r="G42" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H42" s="2" t="s">
+      <c r="G42" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="2">
         <v>45728.0</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G43" s="1">
         <v>15000.0</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="2" t="s">
+      <c r="C44" s="3"/>
+      <c r="D44" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="2">
         <v>45730.0</v>
       </c>
-      <c r="G44" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H44" s="2" t="s">
+      <c r="G44" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="2">
         <v>45397.0</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G45" s="1">
         <v>35000.0</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H45" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="2">
         <v>45404.0</v>
       </c>
-      <c r="G46" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H46" s="2" t="s">
+      <c r="G46" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="2">
         <v>45417.0</v>
       </c>
-      <c r="G47" s="2">
+      <c r="G47" s="1">
         <v>15000.0</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="H47" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="2">
         <v>45424.0</v>
       </c>
-      <c r="G48" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H48" s="2" t="s">
+      <c r="G48" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="2">
         <v>45430.0</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="1">
         <v>5000.0</v>
       </c>
-      <c r="H49" s="2" t="s">
+      <c r="H49" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="2">
         <v>45437.0</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50" s="1">
         <v>35000.0</v>
       </c>
-      <c r="H50" s="2" t="s">
+      <c r="H50" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="2">
         <v>45444.0</v>
       </c>
-      <c r="G51" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="H51" s="2" t="s">
+      <c r="G51" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" s="5">
+        <v>45385.0</v>
+      </c>
+      <c r="G52" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F53" s="5">
+        <v>45389.0</v>
+      </c>
+      <c r="G53" s="4">
+        <v>15000.0</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F54" s="5">
+        <v>45393.0</v>
+      </c>
+      <c r="G54" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" s="5">
+        <v>45397.0</v>
+      </c>
+      <c r="G55" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="5">
+        <v>45401.0</v>
+      </c>
+      <c r="G56" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="5">
+        <v>45405.0</v>
+      </c>
+      <c r="G57" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="5">
+        <v>45409.0</v>
+      </c>
+      <c r="G58" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F59" s="5">
+        <v>45413.0</v>
+      </c>
+      <c r="G59" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F60" s="5">
+        <v>45417.0</v>
+      </c>
+      <c r="G60" s="4">
+        <v>15000.0</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F61" s="5">
+        <v>45421.0</v>
+      </c>
+      <c r="G61" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="5">
+        <v>45425.0</v>
+      </c>
+      <c r="G62" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F63" s="5">
+        <v>45429.0</v>
+      </c>
+      <c r="G63" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" s="5">
+        <v>45433.0</v>
+      </c>
+      <c r="G64" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F65" s="5">
+        <v>45437.0</v>
+      </c>
+      <c r="G65" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F66" s="5">
+        <v>45441.0</v>
+      </c>
+      <c r="G66" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F67" s="5">
+        <v>45445.0</v>
+      </c>
+      <c r="G67" s="4">
+        <v>15000.0</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="5">
+        <v>45449.0</v>
+      </c>
+      <c r="G68" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F69" s="5">
+        <v>45453.0</v>
+      </c>
+      <c r="G69" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="5">
+        <v>45457.0</v>
+      </c>
+      <c r="G70" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F71" s="5">
+        <v>45461.0</v>
+      </c>
+      <c r="G71" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F72" s="5">
+        <v>45465.0</v>
+      </c>
+      <c r="G72" s="4">
+        <v>15000.0</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F73" s="5">
+        <v>45469.0</v>
+      </c>
+      <c r="G73" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" s="5">
+        <v>45473.0</v>
+      </c>
+      <c r="G74" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F75" s="5">
+        <v>45477.0</v>
+      </c>
+      <c r="G75" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F76" s="5">
+        <v>45481.0</v>
+      </c>
+      <c r="G76" s="4">
+        <v>15000.0</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" s="5">
+        <v>45485.0</v>
+      </c>
+      <c r="G77" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F78" s="5">
+        <v>45489.0</v>
+      </c>
+      <c r="G78" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F79" s="5">
+        <v>45493.0</v>
+      </c>
+      <c r="G79" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" s="5">
+        <v>45497.0</v>
+      </c>
+      <c r="G80" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F81" s="5">
+        <v>45501.0</v>
+      </c>
+      <c r="G81" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F82" s="5">
+        <v>45505.0</v>
+      </c>
+      <c r="G82" s="4">
+        <v>15000.0</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F83" s="5">
+        <v>45509.0</v>
+      </c>
+      <c r="G83" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="5">
+        <v>45513.0</v>
+      </c>
+      <c r="G84" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F85" s="5">
+        <v>45517.0</v>
+      </c>
+      <c r="G85" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F86" s="5">
+        <v>45521.0</v>
+      </c>
+      <c r="G86" s="4">
+        <v>15000.0</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F87" s="5">
+        <v>45525.0</v>
+      </c>
+      <c r="G87" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F88" s="5">
+        <v>45529.0</v>
+      </c>
+      <c r="G88" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F89" s="5">
+        <v>45533.0</v>
+      </c>
+      <c r="G89" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F90" s="5">
+        <v>45537.0</v>
+      </c>
+      <c r="G90" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91" s="5">
+        <v>45541.0</v>
+      </c>
+      <c r="G91" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F92" s="5">
+        <v>45545.0</v>
+      </c>
+      <c r="G92" s="4">
+        <v>15000.0</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F93" s="5">
+        <v>45549.0</v>
+      </c>
+      <c r="G93" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F94" s="5">
+        <v>45553.0</v>
+      </c>
+      <c r="G94" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F95" s="5">
+        <v>45557.0</v>
+      </c>
+      <c r="G95" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" s="5">
+        <v>45561.0</v>
+      </c>
+      <c r="G96" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F97" s="5">
+        <v>45565.0</v>
+      </c>
+      <c r="G97" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F98" s="5">
+        <v>45569.0</v>
+      </c>
+      <c r="G98" s="4">
+        <v>15000.0</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F99" s="5">
+        <v>45573.0</v>
+      </c>
+      <c r="G99" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F100" s="5">
+        <v>45577.0</v>
+      </c>
+      <c r="G100" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F101" s="5">
+        <v>45581.0</v>
+      </c>
+      <c r="G101" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="H101" s="4" t="s">
         <v>50</v>
       </c>
     </row>
